--- a/outputs/scenario_campaigns_20260716/01_ad_groups_staging_artifact.xlsx
+++ b/outputs/scenario_campaigns_20260716/01_ad_groups_staging_artifact.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" r:id="R4447ed7d0fd8477f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" r:id="R28ce0ce2d6a14762"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -334,7 +334,7 @@
       <x:c r="O2"/>
       <x:c r="P2"/>
       <x:c r="Q2" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R2"/>
       <x:c r="S2"/>
@@ -373,7 +373,7 @@
       <x:c r="O3"/>
       <x:c r="P3"/>
       <x:c r="Q3" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R3"/>
       <x:c r="S3"/>
@@ -412,7 +412,7 @@
       <x:c r="O4"/>
       <x:c r="P4"/>
       <x:c r="Q4" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R4"/>
       <x:c r="S4"/>
@@ -451,7 +451,7 @@
       <x:c r="O5"/>
       <x:c r="P5"/>
       <x:c r="Q5" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R5"/>
       <x:c r="S5"/>
@@ -490,7 +490,7 @@
       <x:c r="O6"/>
       <x:c r="P6"/>
       <x:c r="Q6" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R6"/>
       <x:c r="S6"/>
@@ -529,7 +529,7 @@
       <x:c r="O7"/>
       <x:c r="P7"/>
       <x:c r="Q7" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R7"/>
       <x:c r="S7"/>
@@ -568,7 +568,7 @@
       <x:c r="O8"/>
       <x:c r="P8"/>
       <x:c r="Q8" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R8"/>
       <x:c r="S8"/>
@@ -607,7 +607,7 @@
       <x:c r="O9"/>
       <x:c r="P9"/>
       <x:c r="Q9" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R9"/>
       <x:c r="S9"/>
@@ -646,7 +646,7 @@
       <x:c r="O10"/>
       <x:c r="P10"/>
       <x:c r="Q10" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R10"/>
       <x:c r="S10"/>
@@ -685,7 +685,7 @@
       <x:c r="O11"/>
       <x:c r="P11"/>
       <x:c r="Q11" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R11"/>
       <x:c r="S11"/>
@@ -724,7 +724,7 @@
       <x:c r="O12"/>
       <x:c r="P12"/>
       <x:c r="Q12" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R12"/>
       <x:c r="S12"/>
@@ -763,7 +763,7 @@
       <x:c r="O13"/>
       <x:c r="P13"/>
       <x:c r="Q13" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R13"/>
       <x:c r="S13"/>
@@ -802,7 +802,7 @@
       <x:c r="O14"/>
       <x:c r="P14"/>
       <x:c r="Q14" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R14"/>
       <x:c r="S14"/>
@@ -841,7 +841,7 @@
       <x:c r="O15"/>
       <x:c r="P15"/>
       <x:c r="Q15" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R15"/>
       <x:c r="S15"/>
@@ -880,7 +880,7 @@
       <x:c r="O16"/>
       <x:c r="P16"/>
       <x:c r="Q16" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R16"/>
       <x:c r="S16"/>
@@ -919,7 +919,7 @@
       <x:c r="O17"/>
       <x:c r="P17"/>
       <x:c r="Q17" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R17"/>
       <x:c r="S17"/>
@@ -958,7 +958,7 @@
       <x:c r="O18"/>
       <x:c r="P18"/>
       <x:c r="Q18" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R18"/>
       <x:c r="S18"/>
@@ -997,7 +997,7 @@
       <x:c r="O19"/>
       <x:c r="P19"/>
       <x:c r="Q19" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R19"/>
       <x:c r="S19"/>
@@ -1036,7 +1036,7 @@
       <x:c r="O20"/>
       <x:c r="P20"/>
       <x:c r="Q20" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R20"/>
       <x:c r="S20"/>
@@ -1075,7 +1075,7 @@
       <x:c r="O21"/>
       <x:c r="P21"/>
       <x:c r="Q21" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R21"/>
       <x:c r="S21"/>
@@ -1114,7 +1114,7 @@
       <x:c r="O22"/>
       <x:c r="P22"/>
       <x:c r="Q22" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R22"/>
       <x:c r="S22"/>
@@ -1153,7 +1153,7 @@
       <x:c r="O23"/>
       <x:c r="P23"/>
       <x:c r="Q23" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R23"/>
       <x:c r="S23"/>
@@ -1192,7 +1192,7 @@
       <x:c r="O24"/>
       <x:c r="P24"/>
       <x:c r="Q24" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R24"/>
       <x:c r="S24"/>
@@ -1231,7 +1231,7 @@
       <x:c r="O25"/>
       <x:c r="P25"/>
       <x:c r="Q25" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R25"/>
       <x:c r="S25"/>
@@ -1270,7 +1270,7 @@
       <x:c r="O26"/>
       <x:c r="P26"/>
       <x:c r="Q26" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R26"/>
       <x:c r="S26"/>
@@ -1309,7 +1309,7 @@
       <x:c r="O27"/>
       <x:c r="P27"/>
       <x:c r="Q27" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R27"/>
       <x:c r="S27"/>
@@ -1348,7 +1348,7 @@
       <x:c r="O28"/>
       <x:c r="P28"/>
       <x:c r="Q28" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R28"/>
       <x:c r="S28"/>
@@ -1387,7 +1387,7 @@
       <x:c r="O29"/>
       <x:c r="P29"/>
       <x:c r="Q29" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R29"/>
       <x:c r="S29"/>
@@ -1426,7 +1426,7 @@
       <x:c r="O30"/>
       <x:c r="P30"/>
       <x:c r="Q30" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R30"/>
       <x:c r="S30"/>
@@ -1465,7 +1465,7 @@
       <x:c r="O31"/>
       <x:c r="P31"/>
       <x:c r="Q31" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R31"/>
       <x:c r="S31"/>
@@ -1504,7 +1504,7 @@
       <x:c r="O32"/>
       <x:c r="P32"/>
       <x:c r="Q32" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R32"/>
       <x:c r="S32"/>
@@ -1543,7 +1543,7 @@
       <x:c r="O33"/>
       <x:c r="P33"/>
       <x:c r="Q33" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R33"/>
       <x:c r="S33"/>
@@ -1582,7 +1582,7 @@
       <x:c r="O34"/>
       <x:c r="P34"/>
       <x:c r="Q34" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R34"/>
       <x:c r="S34"/>
@@ -1621,7 +1621,7 @@
       <x:c r="O35"/>
       <x:c r="P35"/>
       <x:c r="Q35" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R35"/>
       <x:c r="S35"/>
@@ -1660,7 +1660,7 @@
       <x:c r="O36"/>
       <x:c r="P36"/>
       <x:c r="Q36" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R36"/>
       <x:c r="S36"/>
@@ -1699,7 +1699,7 @@
       <x:c r="O37"/>
       <x:c r="P37"/>
       <x:c r="Q37" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R37"/>
       <x:c r="S37"/>
@@ -1738,7 +1738,7 @@
       <x:c r="O38"/>
       <x:c r="P38"/>
       <x:c r="Q38" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R38"/>
       <x:c r="S38"/>
@@ -1777,7 +1777,7 @@
       <x:c r="O39"/>
       <x:c r="P39"/>
       <x:c r="Q39" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R39"/>
       <x:c r="S39"/>
@@ -1816,7 +1816,7 @@
       <x:c r="O40"/>
       <x:c r="P40"/>
       <x:c r="Q40" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R40"/>
       <x:c r="S40"/>
@@ -1855,7 +1855,7 @@
       <x:c r="O41"/>
       <x:c r="P41"/>
       <x:c r="Q41" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R41"/>
       <x:c r="S41"/>
@@ -1894,7 +1894,7 @@
       <x:c r="O42"/>
       <x:c r="P42"/>
       <x:c r="Q42" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R42"/>
       <x:c r="S42"/>
@@ -1933,7 +1933,7 @@
       <x:c r="O43"/>
       <x:c r="P43"/>
       <x:c r="Q43" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R43"/>
       <x:c r="S43"/>
@@ -1972,7 +1972,7 @@
       <x:c r="O44"/>
       <x:c r="P44"/>
       <x:c r="Q44" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R44"/>
       <x:c r="S44"/>
@@ -2011,7 +2011,7 @@
       <x:c r="O45"/>
       <x:c r="P45"/>
       <x:c r="Q45" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R45"/>
       <x:c r="S45"/>
@@ -2050,7 +2050,7 @@
       <x:c r="O46"/>
       <x:c r="P46"/>
       <x:c r="Q46" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R46"/>
       <x:c r="S46"/>
@@ -2089,7 +2089,7 @@
       <x:c r="O47"/>
       <x:c r="P47"/>
       <x:c r="Q47" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R47"/>
       <x:c r="S47"/>
@@ -2128,7 +2128,7 @@
       <x:c r="O48"/>
       <x:c r="P48"/>
       <x:c r="Q48" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R48"/>
       <x:c r="S48"/>
@@ -2167,7 +2167,7 @@
       <x:c r="O49"/>
       <x:c r="P49"/>
       <x:c r="Q49" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R49"/>
       <x:c r="S49"/>
@@ -2206,7 +2206,7 @@
       <x:c r="O50"/>
       <x:c r="P50"/>
       <x:c r="Q50" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R50"/>
       <x:c r="S50"/>
@@ -2245,7 +2245,7 @@
       <x:c r="O51"/>
       <x:c r="P51"/>
       <x:c r="Q51" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R51"/>
       <x:c r="S51"/>
@@ -2284,7 +2284,7 @@
       <x:c r="O52"/>
       <x:c r="P52"/>
       <x:c r="Q52" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R52"/>
       <x:c r="S52"/>
@@ -2323,7 +2323,7 @@
       <x:c r="O53"/>
       <x:c r="P53"/>
       <x:c r="Q53" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R53"/>
       <x:c r="S53"/>
@@ -2362,7 +2362,7 @@
       <x:c r="O54"/>
       <x:c r="P54"/>
       <x:c r="Q54" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R54"/>
       <x:c r="S54"/>
@@ -2401,7 +2401,7 @@
       <x:c r="O55"/>
       <x:c r="P55"/>
       <x:c r="Q55" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R55"/>
       <x:c r="S55"/>
@@ -2440,7 +2440,7 @@
       <x:c r="O56"/>
       <x:c r="P56"/>
       <x:c r="Q56" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R56"/>
       <x:c r="S56"/>
@@ -2479,7 +2479,7 @@
       <x:c r="O57"/>
       <x:c r="P57"/>
       <x:c r="Q57" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R57"/>
       <x:c r="S57"/>
@@ -2518,7 +2518,7 @@
       <x:c r="O58"/>
       <x:c r="P58"/>
       <x:c r="Q58" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R58"/>
       <x:c r="S58"/>
@@ -2557,7 +2557,7 @@
       <x:c r="O59"/>
       <x:c r="P59"/>
       <x:c r="Q59" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R59"/>
       <x:c r="S59"/>
@@ -2596,7 +2596,7 @@
       <x:c r="O60"/>
       <x:c r="P60"/>
       <x:c r="Q60" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R60"/>
       <x:c r="S60"/>
@@ -2635,7 +2635,7 @@
       <x:c r="O61"/>
       <x:c r="P61"/>
       <x:c r="Q61" t="str">
-        <x:v>SCENARIO_10_20260716</x:v>
+        <x:v>SCENARIO_FACILITIES_V2_20260716</x:v>
       </x:c>
       <x:c r="R61"/>
       <x:c r="S61"/>
